--- a/scripts/output/merged_data_5985264.xlsx
+++ b/scripts/output/merged_data_5985264.xlsx
@@ -1428,23 +1428,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Learning Materials and Their Prototypes for Academic Writing Skills: The Needs of Indonesian Lecturers in the Post-COVID-19 Era</t>
+          <t>Developing Teaching Materials of Academic Writing Using Mobile Learning</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>2023</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Q2 as Journal</t>
+          <t>Q3 as Journal</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>European Journal of Educational Research</t>
+          <t>Ingenierie Des Systemes D Information</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1454,40 +1454,40 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hasanudin C.</t>
+          <t>Zulaeha I.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.scopus.com/record/display.uri?eid=2-s2.0-85149837736&amp;origin=resultslist</t>
+          <t>https://www.scopus.com/record/display.uri?eid=2-s2.0-85160911152&amp;origin=resultslist</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://www.scopus.com/sourceid/21100896874</t>
+          <t>https://www.scopus.com/sourceid/21100202935</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Developing Teaching Materials of Academic Writing Using Mobile Learning</t>
+          <t>Learning Materials and Their Prototypes for Academic Writing Skills: The Needs of Indonesian Lecturers in the Post-COVID-19 Era</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>2023</v>
       </c>
       <c r="C6" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Q3 as Journal</t>
+          <t>Q2 as Journal</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ingenierie Des Systemes D Information</t>
+          <t>European Journal of Educational Research</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1497,17 +1497,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Zulaeha I.</t>
+          <t>Hasanudin C.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.scopus.com/record/display.uri?eid=2-s2.0-85160911152&amp;origin=resultslist</t>
+          <t>https://www.scopus.com/record/display.uri?eid=2-s2.0-85149837736&amp;origin=resultslist</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://www.scopus.com/sourceid/21100202935</t>
+          <t>https://www.scopus.com/sourceid/21100896874</t>
         </is>
       </c>
     </row>
@@ -1881,22 +1881,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Women’s Resistance and the Ideology of Patriarchal Hegemony in Ayu Utami’s Novel Larung: A Critical Discourse Analysis</t>
+          <t>Development of Reading Enrichment Books Integrating Humanistic Values and 21st Century Skills for Pre-Service Teachers</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar?q=+intitle:'Women’s Resistance and the Ideology of Patriarchal Hegemony in Ayu Utami’s Novel Larung: A Critical Discourse Analysis'</t>
+          <t>https://scholar.google.com/scholar?q=+intitle:'Development of Reading Enrichment Books Integrating Humanistic Values and 21st Century Skills for Pre-Service Teachers'</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>S Suharyo, A Nuryatin, S Subyantoro, M Doyin</t>
+          <t>P Nurhabibah, S Subyantoro, R Pristiwati, H Haryadi, J Wilson</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>KEMBARA: Jurnal Keilmuan Bahasa, Sastra, dan Pengajarannya 11 (2), 1091-1105, 2025</t>
+          <t>Aptisi Transactions on Technopreneurship (ATT) 7 (3), 1014-1027, 2025</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -1912,22 +1912,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Audio Visual Comics as Resilience for Child and Adolescent Protection from Cyberbullying in the Digital Era</t>
+          <t>The Effectiveness of Learning to Write Drama Texts through Assisted Productive Creative Models Short Film Media and Short Story Text Product Media Based on Student Learning Style</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar?q=+intitle:'Audio Visual Comics as Resilience for Child and Adolescent Protection from Cyberbullying in the Digital Era'</t>
+          <t>https://scholar.google.com/scholar?q=+intitle:'The Effectiveness of Learning to Write Drama Texts through Assisted Productive Creative Models Short Film Media and Short Story Text Product Media Based on Student Learning Style'</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>S Subyantoro, APY Utomo, Z Zuliyanti, AN Wulan</t>
+          <t>R Aulia, S Subyantoro, M Doyin</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Journal of Posthumanism 5 (2), 1403-1416, 2025</t>
+          <t>Seloka: Jurnal Pendidikan Bahasa dan Sastra Indonesia, 45-56, 2025</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -1943,22 +1943,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Development of Reading Enrichment Books Integrating Humanistic Values and 21st Century Skills for Pre-Service Teachers</t>
+          <t>Women’s Resistance and the Ideology of Patriarchal Hegemony in Ayu Utami’s Novel Larung: A Critical Discourse Analysis</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar?q=+intitle:'Development of Reading Enrichment Books Integrating Humanistic Values and 21st Century Skills for Pre-Service Teachers'</t>
+          <t>https://scholar.google.com/scholar?q=+intitle:'Women’s Resistance and the Ideology of Patriarchal Hegemony in Ayu Utami’s Novel Larung: A Critical Discourse Analysis'</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>P Nurhabibah, S Subyantoro, R Pristiwati, H Haryadi, J Wilson</t>
+          <t>S Suharyo, A Nuryatin, S Subyantoro, M Doyin</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aptisi Transactions on Technopreneurship (ATT) 7 (3), 1014-1027, 2025</t>
+          <t>KEMBARA: Jurnal Keilmuan Bahasa, Sastra, dan Pengajarannya 11 (2), 1091-1105, 2025</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -1974,22 +1974,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Effectiveness of Learning to Write Drama Texts through Assisted Productive Creative Models Short Film Media and Short Story Text Product Media Based on Student Learning Style</t>
+          <t>Audio Visual Comics as Resilience for Child and Adolescent Protection from Cyberbullying in the Digital Era</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar?q=+intitle:'The Effectiveness of Learning to Write Drama Texts through Assisted Productive Creative Models Short Film Media and Short Story Text Product Media Based on Student Learning Style'</t>
+          <t>https://scholar.google.com/scholar?q=+intitle:'Audio Visual Comics as Resilience for Child and Adolescent Protection from Cyberbullying in the Digital Era'</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>R Aulia, S Subyantoro, M Doyin</t>
+          <t>S Subyantoro, APY Utomo, Z Zuliyanti, AN Wulan</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Seloka: Jurnal Pendidikan Bahasa dan Sastra Indonesia, 45-56, 2025</t>
+          <t>Journal of Posthumanism 5 (2), 1403-1416, 2025</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -2005,29 +2005,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tren dan dampak penggunaan Kahoot!! dalam pembelajaran bahasa Indonesia: A systematic literature review</t>
+          <t>Pelatihan Mengonversi Hasil Penelitian Menjadi Buku Dan Artikel Ilmiah Sebagai Upaya Peningkatan Gerakan Sadar Reseacrh Literacy Di Sma N 1 Bukateja</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar?q=+intitle:'Tren dan dampak penggunaan Kahoot!! dalam pembelajaran bahasa Indonesia: A systematic literature review'</t>
+          <t>https://scholar.google.com/scholar?q=+intitle:'Pelatihan Mengonversi Hasil Penelitian Menjadi Buku Dan Artikel Ilmiah Sebagai Upaya Peningkatan Gerakan Sadar Reseacrh Literacy Di Sma N 1 Bukateja'</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>S Sukarismanti, S Subyantoro, R Pristiwati, S Samsudin</t>
+          <t>S Suseno, S Subyantoro, QA Neina, Z Zuliyanti, E Kusrini, L Septiani, ...</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jurnal Genre (Bahasa, Sastra, Dan Pembelajarannya) 6 (1), 208-220, 2024</t>
+          <t>Varia Humanika 5 (1), 1-9, 2024</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>2024</v>
       </c>
       <c r="G6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -2036,29 +2036,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>How do Teachers Overcome Failed Interaction After Asking Question?</t>
+          <t>Implementasi proyek penguatan profil pelajar pancasila tema kearifan lokal di SMAN 1 Ile Ape Kabupaten Lembata</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar?q=+intitle:'How do Teachers Overcome Failed Interaction After Asking Question?'</t>
+          <t>https://scholar.google.com/scholar?q=+intitle:'Implementasi proyek penguatan profil pelajar pancasila tema kearifan lokal di SMAN 1 Ile Ape Kabupaten Lembata'</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>MH Rahman, S Subyantoro, T Yuniawan, R Pristiwati</t>
+          <t>KM Lenga, R Pristiwati, S Subyantoro</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Proceedings of International Conference on Science, Education, and …, 2024</t>
+          <t>Jurnal Genre (Bahasa, Sastra, Dan Pembelajarannya) 6 (1), 161-173, 2024</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>2024</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -2067,29 +2067,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Therapeutic fairytales for holistic child development: A systematic literature review of clinical, educational, and family-based practices</t>
+          <t>Evaluasi Pelaksanaan Perkuliahan Semester Antara Menggunakan Model Countenance Stake</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar?q=+intitle:'Therapeutic fairytales for holistic child development: A systematic literature review of clinical, educational, and family-based practices'</t>
+          <t>https://scholar.google.com/scholar?q=+intitle:'Evaluasi Pelaksanaan Perkuliahan Semester Antara Menggunakan Model Countenance Stake'</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>AS Masri, A Nuryatin, S Subyantoro, M Doyin, P Prusdianto</t>
+          <t>AM Susetyo, J Junaidi, V Wardani, S Subyantoro, W Wagiran</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Journal of Mother and Child 28 (1), 136-145, 2024</t>
+          <t>Jurnal Onoma: Pendidikan, Bahasa, dan Sastra 10 (2), 2130-2143, 2024</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>2024</v>
       </c>
       <c r="G8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -2098,29 +2098,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Development of Electronic Media Assisted Language Learning Modules with Cultural Literacy</t>
+          <t>CREATIVE WRITING ON DIGITAL PLATFORMS FOR JOURNALISTIC SUBJECT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar?q=+intitle:'Development of Electronic Media Assisted Language Learning Modules with Cultural Literacy'</t>
+          <t>https://scholar.google.com/scholar?q=+intitle:'CREATIVE WRITING ON DIGITAL PLATFORMS FOR JOURNALISTIC SUBJECT'</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>A Maulana, S Subyantoro, T Yuniawan, R Pristiwati</t>
+          <t>H Nufus, S Subyantoro, HB Mardikantoro, R Pristiwati</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ingenierie des Systemes d'Information 29 (4), 1283, 2024</t>
+          <t>Proceedings of Fine Arts, Literature, Language, and Education, 306-306, 2024</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>2024</v>
       </c>
       <c r="G9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -2129,29 +2129,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PEMBELAJARAN MENULIS CERPEN BERBASIS PLATFORM SASTRA SIBER DI INDONESIA: SELERA INDUSTRI ATAU KEBUTUHAN SENI?</t>
+          <t>Kecerdasan buatan dalam konteks kurikulum merdeka pada jenjang pendidikan dasar dan menengah: Membangun keterampilan menuju Indonesia emas 2045</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar?q=+intitle:'PEMBELAJARAN MENULIS CERPEN BERBASIS PLATFORM SASTRA SIBER DI INDONESIA: SELERA INDUSTRI ATAU KEBUTUHAN SENI?'</t>
+          <t>https://scholar.google.com/scholar?q=+intitle:'Kecerdasan buatan dalam konteks kurikulum merdeka pada jenjang pendidikan dasar dan menengah: Membangun keterampilan menuju Indonesia emas 2045'</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Z Fahmy, R Pristiwati, S Subyantoro</t>
+          <t>S Suharyo, S Subyantoro, R Pristiwati</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paedagoria: Jurnal Kajian, Penelitian dan Pengembangan Kependidikan 15 (1 …, 2024</t>
+          <t>Humanika 30 (2), 208-217, 2024</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>2024</v>
       </c>
       <c r="G10" t="n">
-        <v>10</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11">
@@ -2160,29 +2160,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>OPTIMALISASI PENINGKATAN LITERASI MEMBACA SISWA INDONESIA PADA ERA SOCIETY 5.0 MELALUI PLATFORM PENJARING</t>
+          <t>Peranan guru dalam manajemen peserta didik untuk meningkatkan kualitas peserta didik</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar?q=+intitle:'OPTIMALISASI PENINGKATAN LITERASI MEMBACA SISWA INDONESIA PADA ERA SOCIETY 5.0 MELALUI PLATFORM PENJARING'</t>
+          <t>https://scholar.google.com/scholar?q=+intitle:'Peranan guru dalam manajemen peserta didik untuk meningkatkan kualitas peserta didik'</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>N Widianti, S Subyantoro, R Pristiwati</t>
+          <t>MLK Wati, S Subyantoro, W Wagiran</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ORASI: Jurnal Dakwah dan Komunikasi 15 (1), 2024</t>
+          <t>Jurnal Onoma: Pendidikan, Bahasa, Dan Sastra 10 (1), 1073-1090, 2024</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>2024</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -3176,7 +3176,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Seni menulis teks negosiasi</t>
+          <t>Manajemen pendidikan pada era digital</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Puspita Setyaningrum, Subyantoro, Wagiran</t>
+          <t>Citra Rizky Lestari, Maulida Laily Kusuma Wati, Klemens Maksianus Lenga, Nugraheti Sismulyasih SB, Septina Sulistyaningrum, Dimas Pramata Sukma, [dan 12 lainnya] ; editor, Prof. Dr. Subyantoro, M.Hum., Dr. Wagiran, M.Hum.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PT. Nukilan Media Utama</t>
+          <t>Alinea Edumedia</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -3199,17 +3199,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Semarang</t>
+          <t>Cilacap</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>9786231005250</v>
+        <v>9786231012142</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Peningkatan kinerja bisnis [sumber elektronis] : literasi kesehatan mental dan budaya berbagi pengetahuan bagi klaster UMKM</t>
+          <t>Seni menulis teks negosiasi</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Prof. Dr. Arief Subyantoro, M.S., Dr. Khoirul Hikmah, S.E., M.Si., Dr. Dwi Aulia Puspitaningrum, S.P., M.P., Rifqi Syarif Nasrulloh, S.E., M.M.</t>
+          <t>Puspita Setyaningrum, Subyantoro, Wagiran</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Deepublish Digital</t>
+          <t>PT. Nukilan Media Utama</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -3236,13 +3236,13 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>9786231240897</v>
+        <v>9786231005250</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hoaks atau fakta? yuk, cari tahu dengan belajar membaca teks berita bohong bidang pemerintahan [sumber elektronis]</t>
+          <t>Peningkatan kinerja bisnis [sumber elektronis] : literasi kesehatan mental dan budaya berbagi pengetahuan bagi klaster UMKM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3252,12 +3252,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>penulis, Prof. Dr . Subyantoro, M.Hum., Zuliyanti., S.Pd., M.Pd., Suseno, S.Pd., M.A.</t>
+          <t>Prof. Dr. Arief Subyantoro, M.S., Dr. Khoirul Hikmah, S.E., M.Si., Dr. Dwi Aulia Puspitaningrum, S.P., M.P., Rifqi Syarif Nasrulloh, S.E., M.M.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>UNW Press</t>
+          <t>Deepublish Digital</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>9786231033901</v>
+        <v>9786231240897</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Manajemen pendidikan pada era digital</t>
+          <t>Hoaks atau fakta? yuk, cari tahu dengan belajar membaca teks berita bohong bidang pemerintahan [sumber elektronis]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Citra Rizky Lestari, Maulida Laily Kusuma Wati, Klemens Maksianus Lenga, Nugraheti Sismulyasih SB, Septina Sulistyaningrum, Dimas Pramata Sukma, [dan 12 lainnya] ; editor, Prof. Dr. Subyantoro, M.Hum., Dr. Wagiran, M.Hum.</t>
+          <t>penulis, Prof. Dr . Subyantoro, M.Hum., Zuliyanti., S.Pd., M.Pd., Suseno, S.Pd., M.A.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Alinea Edumedia</t>
+          <t>UNW Press</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -3298,17 +3298,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Cilacap</t>
+          <t>Semarang</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>9786231012142</v>
+        <v>9786231033901</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Transformasi Pendidikan pada Masa Pascapandemi</t>
+          <t>Cyberbullying : kajian konstruksi ujaran di media sosial</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3318,12 +3318,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Prof. Dr. Subyantoro, M.Hum., Prabawati Nurhabibah, Hetilaniar, Meina Febriani, Imaniah Kusuma Rahayu, Rizky Widia Kardika, Zainal Arifin, Uki Hares Yulianti, Hayatun Nufus,Qurrota Ayu Neina, Prasetyo Yuli Kurniawan, Mei Fita Asri Untari,</t>
+          <t>Prof. Dr. Subyantoro, M.Hum. ; editor, Dr. Mintarsih Arbarini, M.Pd.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Cipta Prima Nusantara, CV</t>
+          <t>UNW Press</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -3335,13 +3335,13 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>9786233803113</v>
+        <v>9786230925108</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cyberbullying : kajian konstruksi ujaran di media sosial</t>
+          <t>Transformasi Pendidikan pada Masa Pascapandemi</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3351,12 +3351,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Prof. Dr. Subyantoro, M.Hum. ; editor, Dr. Mintarsih Arbarini, M.Pd.</t>
+          <t>Prof. Dr. Subyantoro, M.Hum., Prabawati Nurhabibah, Hetilaniar, Meina Febriani, Imaniah Kusuma Rahayu, Rizky Widia Kardika, Zainal Arifin, Uki Hares Yulianti, Hayatun Nufus,Qurrota Ayu Neina, Prasetyo Yuli Kurniawan, Mei Fita Asri Untari,</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>UNW Press</t>
+          <t>Cipta Prima Nusantara, CV</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -3368,7 +3368,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>9786230925108</v>
+        <v>9786233803113</v>
       </c>
     </row>
     <row r="8">
